--- a/redirect/glavis-redirect-url-list.xlsx
+++ b/redirect/glavis-redirect-url-list.xlsx
@@ -2910,7 +2910,7 @@
       <c r="G5" s="13" t="n"/>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t>一覧ページ。GA新設「アジェンダ／取り組みテーマ」一覧へ</t>
+          <t>一覧ページ。GA新設「アジェンダ／取組テーマ」一覧へ</t>
         </is>
       </c>
     </row>

--- a/redirect/glavis-redirect-url-list.xlsx
+++ b/redirect/glavis-redirect-url-list.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'①採用サイト'!$A$3:$H$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'②HD記事→GA'!$A$3:$H$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'③HDに残るページ'!$A$3:$F$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'③HDに残るページ'!$A$3:$F$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'④GA既存ページ'!$A$3:$F$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -640,7 +640,7 @@
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>③HDに残るページ（95件）　ニュース・企業情報などHDに残すページです。リダイレクトは不要です。</t>
+          <t>③HDに残るページ（96件）　ニュース・企業情報などHDに残すページです。リダイレクトは不要です。</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5686,7 +5686,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>③HDに残るページ（全95件）　リダイレクト不要</t>
+          <t>③HDに残るページ（全96件）　リダイレクト不要</t>
         </is>
       </c>
     </row>
@@ -8579,8 +8579,38 @@
         </is>
       </c>
     </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="14" t="n">
+        <v>96</v>
+      </c>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/author/</t>
+        </is>
+      </c>
+      <c r="C99" s="16" t="inlineStr">
+        <is>
+          <t>監修者・執筆者一覧｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>ページ(トップ・一覧・固定)</t>
+        </is>
+      </c>
+      <c r="E99" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F99" s="16" t="inlineStr">
+        <is>
+          <t>★CSV未収録のため追加。17名が1ページに並ぶ構成で個人ページはなし。各記事から /author/?author={ID} のクエリ付きURLで該当箇所へ遷移。8/10 方針変更によりHDに残置</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:F98"/>
+  <autoFilter ref="A3:F99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/redirect/glavis-redirect-url-list.xlsx
+++ b/redirect/glavis-redirect-url-list.xlsx
@@ -12,13 +12,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="②HD記事→GA" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③HDに残るページ" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④GA既存ページ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="選択肢" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤クロール追加検出" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="選択肢" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'①採用サイト'!$A$3:$H$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'②HD記事→GA'!$A$3:$H$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'③HDに残るページ'!$A$3:$F$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'④GA既存ページ'!$A$3:$F$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'⑤クロール追加検出'!$A$3:$F$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -561,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B30"/>
+  <dimension ref="B2:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -652,100 +654,107 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>⑤クロール追加検出（72件）　現行サイトの巡回で見つかった、URL一覧CSVに無かったURLです。タグアーカイブ・絞り込みクエリ等で、転送要否のご判断が必要です。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>例外をご指定いただく場合のみ、F列（薄黄）をご変更ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>・案の通りでよい行 → そのまま（初期値「案の通りでOK」）。何もしなくて結構です。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>・転送先を変えたい行 → F列で「変更したい」を選び、G列に転送先URLをご記入ください。</t>
+          <t>・案の通りでよい行 → そのまま（初期値「案の通りでOK」）。何もしなくて結構です。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
+          <t>・転送先を変えたい行 → F列で「変更したい」を選び、G列に転送先URLをご記入ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
           <t>・新サイトに残さないページ → F列で「このページは廃止（トップへ）」を選択してください。</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="3" t="n"/>
-    </row>
     <row r="21">
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>ご参考：特にご確認いただくとよい点</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>・Web広告のリンク先（LP）に使用しているURLがあれば、その行の転送先をご確認ください。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="inlineStr">
         <is>
+          <t>・Web広告のリンク先（LP）に使用しているURLがあれば、その行の転送先をご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
           <t>・②の「GA構築後に確定」の行は、GA側のページができ次第あらためて一覧でご報告いたします。</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="3" t="n"/>
-    </row>
     <row r="25">
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>ご連絡方法（例外がある場合のみ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>このファイルをメールに添付し、下記までご返送ください。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>該当箇所が少なければ、本文に「○○のページは△△へ」とご記入いただくだけでも結構です。</t>
+          <t>このファイルをメールに添付し、下記までご返送ください。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>宛先：tsutomu.kado@mocamoco.com（加堂）／ kodama@itline.co.jp（小玉）</t>
+          <t>該当箇所が少なければ、本文に「○○のページは△△へ」とご記入いただくだけでも結構です。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>件名：【GLAVIS】301リダイレクト転送先のご指定</t>
+          <t>宛先：tsutomu.kado@mocamoco.com（加堂）／ kodama@itline.co.jp（小玉）</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>件名：【GLAVIS】301リダイレクト転送先のご指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Teams のプライベートチャットへの添付でも結構です。</t>
         </is>
@@ -10400,6 +10409,2235 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>⑤クロールで追加検出したURL（全72件）　URL一覧CSVに無かったもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>現行サイトを巡回して見つかったURLです。タグアーカイブ・絞り込みクエリ等。転送要否のご判断が必要です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>現行URL</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>ページタイトル</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>転送先URL（ITLINE設定）</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/000436/index.html</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>社内対談システム調達におけるプロジェクトマネジメントとコンサルタントによる工程管理のあるべき姿【前編】｜GLAVISグループ</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>index.html 付き重複</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>同じ記事にディレクトリ形式でも到達可能。正規URLへ統一が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/000438/index.html</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>社内対談システム調達におけるプロジェクトマネジメントとコンサルタントによる工程管理のあるべき姿【後編】｜GLAVISグループ</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>index.html 付き重複</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>同じ記事にディレクトリ形式でも到達可能。正規URLへ統一が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/ai/</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>生成AI｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/ai_1/</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>公共AIナレッジベース｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/ai_2/</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>AIエージェント｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/bpr/</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>BPR｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/cat113/</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>プロジェクト失敗｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/cat114/</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>問題プロジェクト｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/cat153/</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>デジタルトランスフォーメーション｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/cat161/</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>ガバメントソリューションサービス｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/cat162/</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>基盤システム｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/cat163/</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>政策立案｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/cat164/</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>政策評価｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/cat168/</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>オンライン行政サービス｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/cat172/</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>インフラマネジメント｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/cat173/</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>群マネ｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/cat56/</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>プロジェクトマネジメント｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/cat65/</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>業務効率化｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/cat73/</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>公共サービス｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/cat74/</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>社会インフラ｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/cat76/</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>防災｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/cat77/</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>官民連携｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/dx/</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>防災DX｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/dx_1/</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>自治体DX｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/ebpm/</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>EBPM｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/case/tag/pdca/</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>PDCA｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/cat113/</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>プロジェクト失敗｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/cat114/</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>問題プロジェクト｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/cat127/</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>オープンデータ｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/cat150/</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>官民｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/cat151/</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>マイナンバー｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/cat153/</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>デジタルトランスフォーメーション｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/cat56/</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>プロジェクトマネジメント｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/cat57/</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>行政経営｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/cat61/</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>デジタル人材｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/cat65/</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>業務効率化｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/cat68/</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>デジタル化｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/cat73/</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>公共サービス｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/cat74/</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>社会インフラ｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/cat75/</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>地方創生｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/cat76/</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>防災｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/cat77/</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>官民連携｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/dx/</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>防災DX｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/dx_1/</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>自治体DX｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/tag/it_1/</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>ITシステム｜テーマ別コンテンツ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>タグアーカイブ</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>記事一覧の絞り込みページ。GA側の該当一覧へ転送するか要判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com//service/implementing/</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>ICT基盤・業務システム - 導入フェーズ｜事業内容｜グラビス・アーキテクツ株式会社</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>ダブルスラッシュ</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="inlineStr">
+        <is>
+          <t>サイト内リンクの記述ミス。同一ページに2つのURLで到達できる状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com//service/supplying/</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>ICT基盤・業務システム - 調達フェーズ｜事業内容｜グラビス・アーキテクツ株式会社</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>ダブルスラッシュ</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>サイト内リンクの記述ミス。同一ページに2つのURLで到達できる状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/author/?author=115</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>監修者・執筆者一覧｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>監修者アンカー</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>記事から参照。/author/ に集約されるため個別の転送は不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/author/?author=117</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>監修者・執筆者一覧｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>監修者アンカー</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>記事から参照。/author/ に集約されるため個別の転送は不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/author/?author=213</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>監修者・執筆者一覧｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>監修者アンカー</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F53" s="16" t="inlineStr">
+        <is>
+          <t>記事から参照。/author/ に集約されるため個別の転送は不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/author/?author=341</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>監修者・執筆者一覧｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>監修者アンカー</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>記事から参照。/author/ に集約されるため個別の転送は不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/author/?author=411</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>監修者・執筆者一覧｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>監修者アンカー</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>記事から参照。/author/ に集約されるため個別の転送は不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/author/?author=542</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>監修者・執筆者一覧｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>監修者アンカー</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>記事から参照。/author/ に集約されるため個別の転送は不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/author/?author=570</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr">
+        <is>
+          <t>監修者・執筆者一覧｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>監修者アンカー</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>記事から参照。/author/ に集約されるため個別の転送は不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/author/?author=608</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>監修者・執筆者一覧｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>監修者アンカー</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>記事から参照。/author/ に集約されるため個別の転送は不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/author/?author=637</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="inlineStr">
+        <is>
+          <t>監修者・執筆者一覧｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>監修者アンカー</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F59" s="16" t="inlineStr">
+        <is>
+          <t>記事から参照。/author/ に集約されるため個別の転送は不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/author/?author=660</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>監修者・執筆者一覧｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>監修者アンカー</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>記事から参照。/author/ に集約されるため個別の転送は不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="14" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/company/message/?anchor=message</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
+          <t>代表（古見彰里）メッセージ｜GLAVISグループ</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>絞り込みクエリ</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F61" s="16" t="inlineStr">
+        <is>
+          <t>一覧の絞り込み・アンカー指定。転送要否の判断が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/news/?category=glavisarchitects</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>ニュースリリース・お知らせ｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>絞り込みクエリ</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>一覧の絞り込み・アンカー指定。転送要否の判断が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/download/?post=000170</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="inlineStr">
+        <is>
+          <t>日本の社会問題のインフォグラフィック一覧｜GLAVISグループ</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>絞り込みクエリ</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
+        <is>
+          <t>一覧の絞り込み・アンカー指定。転送要否の判断が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/download/?post=000181</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>日本の社会問題のインフォグラフィック一覧｜GLAVISグループ</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>絞り込みクエリ</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>一覧の絞り込み・アンカー指定。転送要否の判断が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/download/?post=000306</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
+        <is>
+          <t>日本の社会問題のインフォグラフィック一覧｜GLAVISグループ</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>絞り込みクエリ</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>一覧の絞り込み・アンカー指定。転送要否の判断が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="9" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/download/?post=000413</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>日本の社会問題のインフォグラフィック一覧｜GLAVISグループ</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>絞り込みクエリ</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>一覧の絞り込み・アンカー指定。転送要否の判断が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="14" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/download/?post=000429</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>日本の社会問題のインフォグラフィック一覧｜GLAVISグループ</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>絞り込みクエリ</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>一覧の絞り込み・アンカー指定。転送要否の判断が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/download/?post=000476</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>日本の社会問題のインフォグラフィック一覧｜GLAVISグループ</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>絞り込みクエリ</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>一覧の絞り込み・アンカー指定。転送要否の判断が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/case/?theme=implement</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
+        <is>
+          <t>事例｜グラビス・アーキテクツ株式会社</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>絞り込みクエリ</t>
+        </is>
+      </c>
+      <c r="E69" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F69" s="16" t="inlineStr">
+        <is>
+          <t>一覧の絞り込み・アンカー指定。転送要否の判断が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/case/?theme=it</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>事例｜グラビス・アーキテクツ株式会社</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>絞り込みクエリ</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>一覧の絞り込み・アンカー指定。転送要否の判断が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/case/?theme=operation</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="inlineStr">
+        <is>
+          <t>事例｜グラビス・アーキテクツ株式会社</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>絞り込みクエリ</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F71" s="16" t="inlineStr">
+        <is>
+          <t>一覧の絞り込み・アンカー指定。転送要否の判断が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/case/?theme=plan</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>事例｜グラビス・アーキテクツ株式会社</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>絞り込みクエリ</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>一覧の絞り込み・アンカー指定。転送要否の判断が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/case/?theme=procurement</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr">
+        <is>
+          <t>事例｜グラビス・アーキテクツ株式会社</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>絞り込みクエリ</t>
+        </is>
+      </c>
+      <c r="E73" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F73" s="16" t="inlineStr">
+        <is>
+          <t>一覧の絞り込み・アンカー指定。転送要否の判断が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/case/?type=country</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>事例｜グラビス・アーキテクツ株式会社</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>絞り込みクエリ</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>一覧の絞り込み・アンカー指定。転送要否の判断が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/case/?type=municipality</t>
+        </is>
+      </c>
+      <c r="C75" s="16" t="inlineStr">
+        <is>
+          <t>事例｜グラビス・アーキテクツ株式会社</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>絞り込みクエリ</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
+        <is>
+          <t>－（リダイレクト不要）</t>
+        </is>
+      </c>
+      <c r="F75" s="16" t="inlineStr">
+        <is>
+          <t>一覧の絞り込み・アンカー指定。転送要否の判断が必要</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:F75"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/redirect/glavis-redirect-url-list.xlsx
+++ b/redirect/glavis-redirect-url-list.xlsx
@@ -17,8 +17,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'①採用サイト'!$A$3:$H$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'②HD記事→GA'!$A$3:$H$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'③HDに残るページ'!$A$3:$F$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'②HD記事→GA'!$A$3:$H$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'③HDに残るページ'!$A$3:$F$98</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'④GA既存ページ'!$A$3:$F$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'⑤クロール追加検出'!$A$3:$F$75</definedName>
   </definedNames>
@@ -635,14 +635,14 @@
     <row r="12">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>②HD記事→GA（78件）　　　/case/・/social_problem/ の記事。転送先はGA側のページ構築後に確定します（記事移行先の振り分けシートの結果に基づきます）。</t>
+          <t>②HD記事→GA（79件）　　　/case/・/social_problem/ の記事。転送先はGA側のページ構築後に確定します（記事移行先の振り分けシートの結果に基づきます）。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>③HDに残るページ（96件）　ニュース・企業情報などHDに残すページです。リダイレクトは不要です。</t>
+          <t>③HDに残るページ（95件）　ニュース・企業情報などHDに残すページです。リダイレクトは不要です。</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2798,7 +2798,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>②HD→GA集約の対象（全78件）　記事・一覧ページ</t>
+          <t>②HD→GA集約の対象（全79件）　記事・一覧ページ</t>
         </is>
       </c>
     </row>
@@ -5659,15 +5659,51 @@
         </is>
       </c>
     </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/author/</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>監修者・執筆者一覧｜GLAVIS（グラビス）グループ</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>ページ(トップ・一覧・固定)</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/member/</t>
+        </is>
+      </c>
+      <c r="F82" s="13" t="inlineStr">
+        <is>
+          <t>案の通りでOK</t>
+        </is>
+      </c>
+      <c r="G82" s="13" t="n"/>
+      <c r="H82" s="11" t="inlineStr">
+        <is>
+          <t>★CSV未収録のため追加。17名が1ページに並ぶ構成で個人ページはなし。8/13 岡田様ご判断によりGA「コンサルタント」へ統合。各記事からの /author/?author={ID} はクエリ単位での転送設定が必要</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:H81"/>
-  <conditionalFormatting sqref="G4:G81">
+  <autoFilter ref="A3:H82"/>
+  <conditionalFormatting sqref="G4:G82">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>LEFT($F4,4)="変更したい"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F4:F81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ご回答" error="プルダウンからお選びください" type="list">
+    <dataValidation sqref="F4:F82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ご回答" error="プルダウンからお選びください" type="list">
       <formula1>=選択肢!$A$1:$A$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -5681,7 +5717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5695,7 +5731,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>③HDに残るページ（全96件）　リダイレクト不要</t>
+          <t>③HDに残るページ（全95件）　リダイレクト不要</t>
         </is>
       </c>
     </row>
@@ -8588,38 +8624,8 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="14" t="n">
-        <v>96</v>
-      </c>
-      <c r="B99" s="15" t="inlineStr">
-        <is>
-          <t>https://www.glavis-hd.com/author/</t>
-        </is>
-      </c>
-      <c r="C99" s="16" t="inlineStr">
-        <is>
-          <t>監修者・執筆者一覧｜GLAVIS（グラビス）グループ</t>
-        </is>
-      </c>
-      <c r="D99" s="14" t="inlineStr">
-        <is>
-          <t>ページ(トップ・一覧・固定)</t>
-        </is>
-      </c>
-      <c r="E99" s="14" t="inlineStr">
-        <is>
-          <t>－（リダイレクト不要）</t>
-        </is>
-      </c>
-      <c r="F99" s="16" t="inlineStr">
-        <is>
-          <t>★CSV未収録のため追加。17名が1ページに並ぶ構成で個人ページはなし。各記事から /author/?author={ID} のクエリ付きURLで該当箇所へ遷移。8/10 方針変更によりHDに残置</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:F99"/>
+  <autoFilter ref="A3:F98"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/redirect/glavis-redirect-url-list.xlsx
+++ b/redirect/glavis-redirect-url-list.xlsx
@@ -5691,7 +5691,7 @@
       <c r="G82" s="13" t="n"/>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>★CSV未収録のため追加。17名が1ページに並ぶ構成で個人ページはなし。8/13 岡田様ご判断によりGA「コンサルタント」へ統合。各記事からの /author/?author={ID} はクエリ単位での転送設定が必要</t>
+          <t>★CSV未収録のため追加。17名が1ページに並ぶ構成で個人ページはなし。8/13 岡田様ご判断によりGA「コンサルタント」配下へ移設（個人ページと並列）。各記事からの /author/?author={ID} はクエリ単位での転送設定が必要</t>
         </is>
       </c>
     </row>
